--- a/Hardware BOM/STAIR Array Hardware BOM.xlsx
+++ b/Hardware BOM/STAIR Array Hardware BOM.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Justin\Desktop\Acoustigrammetry\Hardware BOM\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{071EFD26-159C-461B-AEBE-D59576E54E76}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B3E3DD0C-D5A2-4E38-99AA-FF49F4199BF5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="34620" windowHeight="14620" xr2:uid="{89283368-D86B-449D-9D9F-59E05109387F}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="29" uniqueCount="28">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="46" uniqueCount="41">
   <si>
     <t>STAIR Array BOM</t>
   </si>
@@ -53,9 +53,6 @@
     <t>Source</t>
   </si>
   <si>
-    <t>Umik-X</t>
-  </si>
-  <si>
     <t>Manufacturer</t>
   </si>
   <si>
@@ -101,9 +98,6 @@
     <t>Raspberry Pi Zero 2W</t>
   </si>
   <si>
-    <t>x" spring</t>
-  </si>
-  <si>
     <t>Elastic bands</t>
   </si>
   <si>
@@ -120,13 +114,58 @@
   </si>
   <si>
     <t>Cable ties to interconnect frame faces &amp; manage cables</t>
+  </si>
+  <si>
+    <t>60mm spring</t>
+  </si>
+  <si>
+    <t>80mm spring</t>
+  </si>
+  <si>
+    <t>miniDSP</t>
+  </si>
+  <si>
+    <t>misc.</t>
+  </si>
+  <si>
+    <t>Shockmounts for mic boards</t>
+  </si>
+  <si>
+    <t>16 Omnidirectional Knowles MEMS mic breakout boards, 5 A2B interface boxes</t>
+  </si>
+  <si>
+    <t>T1-2025SC</t>
+  </si>
+  <si>
+    <t>UMIK-X w/ 4 x UMA-XL modules</t>
+  </si>
+  <si>
+    <t>https://www.minidsp.com/products/acoustic-measurement/umik-x-multichannel-mic</t>
+  </si>
+  <si>
+    <t>https://www.parts-express.com/Tang-Band-T1-2025SC-1-5-8-Full-Range-Speaker-Module-264-939?quantity=1&amp;irclickid=yYEw3DxVixyZRr%3A0FMWzDRlWUkuwkOxvPx2yzY0&amp;utm_source=Impact&amp;utm_medium=Impact&amp;utm_campaign=Impact&amp;irgwc=1&amp;afsrc=1</t>
+  </si>
+  <si>
+    <t>https://www.adafruit.com/product/3006</t>
+  </si>
+  <si>
+    <t>MAX98357A</t>
+  </si>
+  <si>
+    <t>Raspberry Pi Foundation</t>
+  </si>
+  <si>
+    <t>The Wehrmeyer Group, LLC</t>
+  </si>
+  <si>
+    <t>https://craftcloud3d.com/</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -146,6 +185,14 @@
       <color theme="0"/>
       <name val="Arial"/>
       <family val="2"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="3">
@@ -171,17 +218,25 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -517,11 +572,12 @@
   <dimension ref="A1:E16"/>
   <sheetFormatPr defaultRowHeight="15.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="31.7265625" style="1" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="31.7265625" style="3" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="58.26953125" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="9.26953125" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="16384" width="8.7265625" style="1"/>
+    <col min="4" max="4" width="29" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="73.1796875" style="3" customWidth="1"/>
+    <col min="6" max="16384" width="8.7265625" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="18" x14ac:dyDescent="0.4">
@@ -534,7 +590,7 @@
       <c r="E1" s="2"/>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A2" s="1" t="s">
+      <c r="A2" s="3" t="s">
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
@@ -544,146 +600,209 @@
         <v>2</v>
       </c>
       <c r="D2" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="E2" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" ht="31" x14ac:dyDescent="0.35">
+      <c r="A3" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C3" s="1">
+        <v>1</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="E3" s="4" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A4" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="B4" s="1" t="s">
         <v>6</v>
-      </c>
-      <c r="E2" s="1" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A3" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="B4" s="1" t="s">
-        <v>7</v>
       </c>
       <c r="C4" s="1">
         <v>8</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
+      </c>
+      <c r="E4" s="4" t="s">
+        <v>36</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.35">
       <c r="B5" s="1" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C5" s="1">
         <v>4</v>
       </c>
+      <c r="D5" s="1" t="s">
+        <v>29</v>
+      </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.35">
       <c r="B6" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C6" s="1">
         <v>4</v>
       </c>
-    </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="D6" s="1" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" ht="58" x14ac:dyDescent="0.35">
+      <c r="A7" s="3" t="s">
+        <v>32</v>
+      </c>
       <c r="B7" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C7" s="1">
+        <v>8</v>
+      </c>
+      <c r="D7" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="E7" s="4" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A8" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="B8" s="1" t="s">
         <v>10</v>
-      </c>
-      <c r="D7" s="1" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A8" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="B8" s="1" t="s">
-        <v>11</v>
       </c>
       <c r="C8" s="1">
         <v>16</v>
       </c>
+      <c r="D8" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="E8" s="4" t="s">
+        <v>40</v>
+      </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A9" s="1" t="s">
-        <v>13</v>
+      <c r="A9" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>10</v>
       </c>
       <c r="C9" s="1">
         <v>2</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A10" s="1" t="s">
-        <v>14</v>
+      <c r="A10" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>10</v>
       </c>
       <c r="C10" s="1">
         <v>1</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A11" s="1" t="s">
+      <c r="A11" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="B11" s="1" t="s">
         <v>17</v>
-      </c>
-      <c r="B11" s="1" t="s">
-        <v>18</v>
       </c>
       <c r="C11" s="1">
         <v>1</v>
       </c>
+      <c r="D11" s="1" t="s">
+        <v>38</v>
+      </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A12" s="1" t="s">
-        <v>20</v>
+      <c r="A12" s="3" t="s">
+        <v>19</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C12" s="1">
         <v>4</v>
       </c>
+      <c r="D12" s="1" t="s">
+        <v>38</v>
+      </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A13" s="1" t="s">
+      <c r="A13" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="B13" s="1" t="s">
         <v>21</v>
-      </c>
-      <c r="B13" s="1" t="s">
-        <v>23</v>
       </c>
       <c r="C13" s="1">
         <v>2</v>
       </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A14" s="1" t="s">
-        <v>21</v>
+      <c r="A14" s="3" t="s">
+        <v>26</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="C14" s="1">
         <v>8</v>
       </c>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A15" s="3" t="s">
+        <v>20</v>
+      </c>
       <c r="B15" s="1" t="s">
-        <v>22</v>
+        <v>30</v>
       </c>
       <c r="C15" s="1">
         <v>32</v>
       </c>
+      <c r="D15" s="1" t="s">
+        <v>29</v>
+      </c>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A16" s="1" t="s">
-        <v>26</v>
+      <c r="A16" s="3" t="s">
+        <v>24</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:E1"/>
   </mergeCells>
+  <hyperlinks>
+    <hyperlink ref="E3" r:id="rId1" xr:uid="{A059BC0D-FC64-4DFC-B90D-370BDF3DB1A5}"/>
+    <hyperlink ref="E7" r:id="rId2" xr:uid="{8F7138F5-CF0C-4733-B089-818AF527EF9C}"/>
+    <hyperlink ref="E4" r:id="rId3" xr:uid="{D2A95AA0-2FA7-4584-B66B-ACB1D9F1DB91}"/>
+    <hyperlink ref="E8" r:id="rId4" xr:uid="{C353E80A-E7EC-4425-9A0F-75CB25050590}"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>